--- a/evaluation/Häufigkeiten_Orte_gesamt.xlsx
+++ b/evaluation/Häufigkeiten_Orte_gesamt.xlsx
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+  <si>
+    <t xml:space="preserve">Paris</t>
+  </si>
   <si>
     <t xml:space="preserve">Frankreich</t>
   </si>
@@ -31,202 +34,166 @@
     <t xml:space="preserve">France</t>
   </si>
   <si>
-    <t xml:space="preserve">Paris</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bourbonne</t>
   </si>
   <si>
+    <t xml:space="preserve">England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Europe</t>
   </si>
   <si>
-    <t xml:space="preserve">Clarens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijon</t>
+    <t xml:space="preserve">Montmorency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holland</t>
   </si>
   <si>
     <t xml:space="preserve">Nantes</t>
   </si>
   <si>
-    <t xml:space="preserve">Frankreichs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Orléans</t>
   </si>
   <si>
     <t xml:space="preserve">Versailles</t>
   </si>
   <si>
-    <t xml:space="preserve">Pariser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montmorency</t>
+    <t xml:space="preserve">“L'Hermitage' </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">australische</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxerre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bastille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bastillehaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berliner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besançon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bordeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bougainville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourbonnewill</t>
   </si>
   <si>
     <t xml:space="preserve">burgundischer</t>
   </si>
   <si>
-    <t xml:space="preserve">Paris“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">australische</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagno</t>
+    <t xml:space="preserve">Café</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chablais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eldorado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gießen'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ile-de-St-Pierre</t>
   </si>
   <si>
     <t xml:space="preserve">Indischen</t>
   </si>
   <si>
-    <t xml:space="preserve">Frankreich.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montmorency.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corse</t>
-  </si>
-  <si>
     <t xml:space="preserve">Korsikas“</t>
   </si>
   <si>
+    <t xml:space="preserve">La</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lac'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lejeune:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lobrede</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marseille.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meillerie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petersburger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polens“</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pologne</t>
   </si>
   <si>
-    <t xml:space="preserve">Polens“</t>
+    <t xml:space="preserve">Rhône</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sachsen-Gotha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schweizer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siegen'</t>
   </si>
   <si>
     <t xml:space="preserve">Tahiti</t>
   </si>
   <si>
-    <t xml:space="preserve">Lobrede</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petersburger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bourbonne“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bourbonnewill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gießen'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Café</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bordeaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Besançon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marseille.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auxerre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bastillehaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Englands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bastille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Europas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berliner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sachsen-Gotha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frankreichzentrierte</t>
-  </si>
-  <si>
     <t xml:space="preserve">Übersee</t>
   </si>
   <si>
     <t xml:space="preserve">Utopia</t>
   </si>
   <si>
-    <t xml:space="preserve">Bougainville</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eldorado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siegen'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schweizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“L'Hermitage' </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhône</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vaud</t>
   </si>
   <si>
-    <t xml:space="preserve">Chablais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meillerie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haus</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wolmarschen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarens.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genf.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ile-de-St-Pierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lac'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lejeune:</t>
   </si>
 </sst>
 </file>
@@ -322,7 +289,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.59"/>
@@ -334,7 +301,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -342,7 +309,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -350,7 +317,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -358,28 +325,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>4</v>
@@ -387,15 +354,15 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>3</v>
@@ -403,15 +370,15 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>2</v>
@@ -419,7 +386,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>2</v>
@@ -427,7 +394,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>2</v>
@@ -435,7 +402,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>2</v>
@@ -443,71 +410,71 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>1</v>
@@ -515,7 +482,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>1</v>
@@ -523,7 +490,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>1</v>
@@ -531,7 +498,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>1</v>
@@ -539,7 +506,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>1</v>
@@ -547,7 +514,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>1</v>
@@ -555,7 +522,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>1</v>
@@ -563,7 +530,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>1</v>
@@ -571,7 +538,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>1</v>
@@ -579,7 +546,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>1</v>
@@ -587,7 +554,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>1</v>
@@ -595,7 +562,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>1</v>
@@ -603,7 +570,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>1</v>
@@ -611,7 +578,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>1</v>
@@ -619,7 +586,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>1</v>
@@ -627,7 +594,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>1</v>
@@ -635,7 +602,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>1</v>
@@ -643,7 +610,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>1</v>
@@ -651,7 +618,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>1</v>
@@ -659,7 +626,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>1</v>
@@ -667,7 +634,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>1</v>
@@ -675,7 +642,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>1</v>
@@ -683,7 +650,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>1</v>
@@ -691,7 +658,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>1</v>
@@ -699,7 +666,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>1</v>
@@ -707,7 +674,7 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>1</v>
@@ -715,7 +682,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>1</v>
@@ -723,7 +690,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>1</v>
@@ -731,7 +698,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>1</v>
@@ -739,7 +706,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>1</v>
@@ -747,7 +714,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>1</v>
@@ -755,7 +722,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>1</v>
@@ -763,7 +730,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>1</v>
@@ -771,7 +738,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>1</v>
@@ -779,7 +746,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>1</v>
@@ -787,185 +754,9 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B60" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B74" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B75" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B78" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="B79" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B80" s="0" t="n">
         <v>1</v>
       </c>
     </row>
